--- a/file/table/SubbasinW2PMax24hr2_33vsPtotal.xlsx
+++ b/file/table/SubbasinW2PMax24hr2_33vsPtotal.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30304"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WREM\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E85F639B-5F39-476B-A3F1-1EAE4D341357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9310AD66-E318-4FFC-81EC-7B9427EF2A84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" xr2:uid="{D5B24722-2EFA-4C84-86FE-1D62E8B2A16C}"/>
   </bookViews>
@@ -1357,16 +1357,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>243416</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>281516</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>4233</xdr:rowOff>
+      <xdr:rowOff>143933</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>563032</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>601133</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>33867</xdr:rowOff>
+      <xdr:rowOff>173567</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
